--- a/data/proteomics/organell protein volume ratio relative to total protein volume from Jianye.xlsx
+++ b/data/proteomics/organell protein volume ratio relative to total protein volume from Jianye.xlsx
@@ -511,22 +511,22 @@
         <v>0.4701297768070277</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2668677881882346</v>
+        <v>0.2668677881882349</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2883727858728327</v>
+        <v>0.288372785872833</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02687342888336699</v>
+        <v>0.026873428883367</v>
       </c>
       <c r="G2" t="n">
         <v>0.004159456798244613</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0412694221134305</v>
+        <v>0.04126942211343047</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04237781230942052</v>
+        <v>0.04237781230942056</v>
       </c>
       <c r="J2" t="n">
         <v>0.01017725237483297</v>
@@ -535,7 +535,7 @@
         <v>0.06788965558869176</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00305322948598601</v>
+        <v>0.003053229485986011</v>
       </c>
       <c r="M2" t="n">
         <v>0.003934165110929628</v>
@@ -555,16 +555,16 @@
         <v>0.044</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4697312362062084</v>
+        <v>0.4697312362062082</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2542450068872546</v>
+        <v>0.254245006887254</v>
       </c>
       <c r="E3" t="n">
         <v>0.2894209109898178</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02813999011241572</v>
+        <v>0.02813999011241568</v>
       </c>
       <c r="G3" t="n">
         <v>0.003753809359885017</v>
@@ -579,10 +579,10 @@
         <v>0.01012432413508245</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07178007246901852</v>
+        <v>0.07178007246901859</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003053830579309739</v>
+        <v>0.00305383057930974</v>
       </c>
       <c r="M3" t="n">
         <v>0.004693939129684316</v>
@@ -602,31 +602,31 @@
         <v>0.102</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4427010824280561</v>
+        <v>0.4427010824280564</v>
       </c>
       <c r="D4" t="n">
-        <v>0.225750304918102</v>
+        <v>0.2257503049181022</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2611804991616697</v>
+        <v>0.2611804991616698</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03140749065292335</v>
+        <v>0.03140749065292332</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002801861753727941</v>
+        <v>0.002801861753727942</v>
       </c>
       <c r="H4" t="n">
         <v>0.03753087297949353</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0341747763038892</v>
+        <v>0.03417477630388924</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009139129970847213</v>
+        <v>0.009139129970847207</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08744541242854886</v>
+        <v>0.08744541242854884</v>
       </c>
       <c r="L4" t="n">
         <v>0.003296633938797981</v>
@@ -638,7 +638,7 @@
         <v>0.0004268286038943762</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02311286167134515</v>
+        <v>0.02311286167134514</v>
       </c>
     </row>
     <row r="5">
@@ -649,10 +649,10 @@
         <v>0.152</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4302917210149803</v>
+        <v>0.4302917210149795</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2117453172515465</v>
+        <v>0.2117453172515461</v>
       </c>
       <c r="E5" t="n">
         <v>0.2475798672246243</v>
@@ -670,10 +670,10 @@
         <v>0.02967937106548232</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008491456951512039</v>
+        <v>0.008491456951512042</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09740055322390193</v>
+        <v>0.09740055322390198</v>
       </c>
       <c r="L5" t="n">
         <v>0.003217073934875056</v>
@@ -685,7 +685,7 @@
         <v>0.0004451542987115833</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02509641747711692</v>
+        <v>0.02509641747711691</v>
       </c>
     </row>
     <row r="6">
@@ -699,13 +699,13 @@
         <v>0.4192303059018092</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1987796473186527</v>
+        <v>0.1987796473186526</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2299264514502334</v>
+        <v>0.2299264514502333</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02776260699003847</v>
+        <v>0.02776260699003846</v>
       </c>
       <c r="G6" t="n">
         <v>0.001743041991028365</v>
@@ -717,13 +717,13 @@
         <v>0.02299061351725481</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008362726574660938</v>
+        <v>0.008362726574660934</v>
       </c>
       <c r="K6" t="n">
         <v>0.1081802839678998</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003224878040109921</v>
+        <v>0.00322487804010992</v>
       </c>
       <c r="M6" t="n">
         <v>0.009706405976719637</v>
@@ -732,7 +732,7 @@
         <v>0.0004826770275208746</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02783189691965789</v>
+        <v>0.02783189691965788</v>
       </c>
     </row>
     <row r="7">
@@ -746,13 +746,13 @@
         <v>0.4139235092300421</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1890869734863404</v>
+        <v>0.1890869734863403</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2189298888844606</v>
+        <v>0.2189298888844607</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02441863224440297</v>
+        <v>0.02441863224440296</v>
       </c>
       <c r="G7" t="n">
         <v>0.001518307409269101</v>
@@ -779,7 +779,7 @@
         <v>0.0005290056095705115</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02925917250358857</v>
+        <v>0.02925917250358859</v>
       </c>
     </row>
     <row r="8">
@@ -793,10 +793,10 @@
         <v>0.4099292536350622</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1882128783430856</v>
+        <v>0.1882128783430859</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2247253380687526</v>
+        <v>0.2247253380687525</v>
       </c>
       <c r="F8" t="n">
         <v>0.02216655956140193</v>
@@ -805,16 +805,16 @@
         <v>0.00155074115160528</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02276163018435192</v>
+        <v>0.02276163018435191</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02156503475702056</v>
+        <v>0.02156503475702055</v>
       </c>
       <c r="J8" t="n">
         <v>0.007135654045493678</v>
       </c>
       <c r="K8" t="n">
-        <v>0.12146303340133</v>
+        <v>0.1214630334013299</v>
       </c>
       <c r="L8" t="n">
         <v>0.003027496977310177</v>
@@ -826,7 +826,7 @@
         <v>0.0006022402036714483</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03029590507927846</v>
+        <v>0.03029590507927845</v>
       </c>
     </row>
     <row r="9">
@@ -840,28 +840,28 @@
         <v>0.3879590819203286</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1907120981083608</v>
+        <v>0.1907120981083607</v>
       </c>
       <c r="E9" t="n">
         <v>0.2207414109251293</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02117371274387799</v>
+        <v>0.02117371274387798</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001401141914034413</v>
+        <v>0.001401141914034414</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02256622037028606</v>
+        <v>0.02256622037028605</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02313607226291884</v>
+        <v>0.02313607226291885</v>
       </c>
       <c r="J9" t="n">
         <v>0.005194150269737435</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1369363309152135</v>
+        <v>0.1369363309152134</v>
       </c>
       <c r="L9" t="n">
         <v>0.002909682476050968</v>
@@ -887,7 +887,7 @@
         <v>0.3704877658802759</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1938642856566679</v>
+        <v>0.193864285656668</v>
       </c>
       <c r="E10" t="n">
         <v>0.2192887908827605</v>
@@ -896,13 +896,13 @@
         <v>0.02112572852349294</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001415795468282523</v>
+        <v>0.001415795468282524</v>
       </c>
       <c r="H10" t="n">
         <v>0.0225530143950937</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02496882645357304</v>
+        <v>0.02496882645357303</v>
       </c>
       <c r="J10" t="n">
         <v>0.004444439224117257</v>
@@ -920,7 +920,7 @@
         <v>0.0005631399825533625</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0336408487969829</v>
+        <v>0.03364084879698288</v>
       </c>
     </row>
   </sheetData>
